--- a/human_validation/judge/kor/judge_D014_S002_P001__gemini-3.8-flash_kor.xlsx
+++ b/human_validation/judge/kor/judge_D014_S002_P001__gemini-3.8-flash_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B66"/>
+  <dimension ref="A1:B59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,313 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요. 오늘 병원에 오시게 된 이유가 무엇인가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 제가 온 이유는 수면이 오랫동안 정말 엉망이었기 때문이에요. 지쳐서 침대에 쓰러지긴 하는데, 집 안의 작은 소리 하나에도 깨고, 그러다 알람이 울리기도 전에 이미 깨어 있어요. 그냥 쉰 것 같은 느낌이 전혀 안 들어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 피곤한 것 외에, 지속적으로 가라앉거나 슬프거나 절망적인 느낌을 받으셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 네. 대부분의 날에는 뭔가 색이 다 빠져나간 느낌이에요. 가족들과의 일요일 저녁 식사에서도, 예전에 좋아하던 미술 작품을 볼 때도, 별로 아무것도 느껴지지 않아요. 그리고 가끔은 이유를 정확히 설명할 수는 없는데 눈물을 참느라 애써야 할 때도 있어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 이렇게 가라앉고 다른 일들과 단절된 느낌을 얼마나 오래 느껴오셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 이제 2년이 조금 넘었어요—시어머니가 저희 집으로 들어오신 이후부터요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 지난 2년 동안, 2개월 이상 평소의 자신으로 돌아왔다고 느낀 시기가 있었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 아니요, 그렇게 오래 예전의 저로 돌아왔다고 느낀 적은 없었어요. 시어머니가 들어오신 이후로 계속 이랬어요, 2년이 조금 넘었네요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 2년 전 이 일이 시작되기 전에도 살면서 상당히 우울했던 시기가 있었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] 잘 모르겠어요. 이런 느낌이었던 다른 시기는 딱히 떠오르지 않아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사 질문] 이 기간 동안 무가치감이나 과도한 죄책감으로 힘드셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 환자 응답] 잘 모르겠어요. 특별히 죄책감이나 무가치감을 느낀 적은 없는 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사 질문] 삶이 살 가치가 없다는 생각이나 자해에 대한 생각을 하신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 환자 응답] 정확히 무슨 뜻이신지 잘 모르겠어요. 그런 생각을 한 적은 딱히 없는 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사의 감별진단] 범불안장애 (D011); 지속성 우울장애 (D014); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사 질문] 이 기간 동안 식욕이나 체중에 변화가 있으셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 환자 응답] 네. 요즘엔 식욕이 그다지 없어요. 대부분 다른 사람들을 위해 만든 음식을 조금씩 집어 먹거나, 근무 끝나고 토스트 정도 먹어요. 옷이 점점 헐렁해지고 있는데, 일부러 살을 빼려던 게 아니었어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사의 감별진단] 지속성 우울장애 (D014) | 범불안장애 (D011); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사 질문] 집중하거나 초점을 맞추거나 일상적인 결정을 내리는 데 어려움을 느끼신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 환자 응답] 딱히 그런 실질적인 문제를 느낀 것 같지는 않아요. 그러니까, 평소 결정 같은 건 그럭저럭 해나가고 있어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사의 감별진단] 지속성 우울장애 (D014) | 범불안장애 (D011); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사 질문] 본인이나 주변 사람들이 평소보다 움직임이나 말이 훨씬 느려졌다고 느낀 적이 있나요, 아니면 반대로 이유 없이 안절부절못하고 가만히 있지 못하는 느낌이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 환자 응답] 제가 움직이거나 말하는 게 느려졌다고 느낀 적은 없어요. 그리고 특별히 안절부절못하는 느낌도 없고요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사의 감별진단] 지속성 우울장애 (D014) | 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사 질문] 미래에 대해 절망적이거나 상황이 나아지지 않을 거라는 느낌이 드시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 환자 응답] 네, 그런 것 같아요. 대부분의 날에는 모든 것에서 색이 빠져나간 느낌이에요. 가족들과의 일요일 저녁 식사에서도, 예전에 좋아하던 미술 작품을 볼 때도, 그냥... 무덤덤해요. 그리고 이유 없이 눈물이 나려는 걸 참으려고 애써야 해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사의 감별진단] 지속성 우울장애 (D014) | 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사 질문] 수면이 끊기는 것 외에도, 낮 동안 에너지가 낮거나 지속적으로 피로감을 느끼신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 환자 응답] 네. 재택 간병 고객분들 보고 집에 돌아와서 그쪽 일까지 도와드리고 나면, 몸이 정말 무겁게 느껴져요. 차팅을 하거나 빨래를 개는 것도 억지로 해야 할 만큼 힘들게 느껴져요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사의 감별진단] 지속성 우울장애 (D014) | 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사 질문] 이 기간 동안 자존감이나 자신감은 어떠셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 환자 응답] 어떻게 판단해야 할지 잘 모르겠어요. 그냥 요즘 스스로에 대해 좋게 느끼는 게 힘들다는 것만 알아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사의 감별진단] 지속성 우울장애 (D014) | 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 의사 질문] 평소보다 훨씬 적은 수면으로도 괜찮을 만큼 비정상적으로 들뜨거나 활력이 넘치는 시기가 있으셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 환자 응답] 그런 것 같지 않아요. 비정상적으로 들뜨거나 잠을 거의 필요로 하지 않았던 시기는 기억나지 않아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 의사의 감별진단] 지속성 우울장애 (D014) | 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 배제됨: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
         <is>
           <t>진단명: 지속성 우울장애 (D014)
 인구통계: 성별 여성 / 나이 53 / 직업상태 home health aide / 최종학력 대학 재학
@@ -575,362 +873,37 @@
 증상 지속 기간: None
 추가 요건: 
 주호소 증상 코드: S027
-배경 서술: 2년 4개월 전, 란의 시어머니의 건강이 악화되면서 란과 남편의 집으로 들어오게 되었고, 이는 유급 재택 간병 근무가 끝난 후 란의 전문 간병 기술을 24시간 가족 책임으로 바꾸어 놓았다. 처음에 란은 이 변화를 자신의 가족 가치관에 맞는 당연한 의무로 받아들였지만, 시간이 지나면서 박물관 방문, 등산, 서예, 자원봉사 미술 워크숍이 점차 밀려났고, 기분은 계속 가라앉아 있었으며, 식습관과 수면 패턴이 바뀌었고, 피로감이 직장과 집 양쪽에서 그녀를 따라다녔다. 그녀가 신입 요양보호사 멘토링을 줄이고 평소와 다르게 서류 작성을 미루기 시작하면서 상태는 임상적으로 유의미해졌고, 남편은 매주 이어지던 가족 저녁 식사조차 더 이상 그녀를 회복시켜주지 못한다는 것을 알아차렸다. 지속적인 탈진을 이유로 한 1차 진료 방문이 의뢰로 이어지면서 그녀는 정신과 진료를 받게 되었고, 그 시점에서 기능 손상을 동반한 2년 4개월간의 지속적인 우울 경과가 명확해졌다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요. 오늘 병원에 오시게 된 이유가 무엇인가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 제가 온 이유는 수면이 오랫동안 정말 엉망이었기 때문이에요. 지쳐서 침대에 쓰러지긴 하는데, 집 안의 작은 소리 하나에도 깨고, 그러다 알람이 울리기도 전에 이미 깨어 있어요. 그냥 쉰 것 같은 느낌이 전혀 안 들어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 피곤한 것 외에, 지속적으로 가라앉거나 슬프거나 절망적인 느낌을 받으셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 네. 대부분의 날에는 뭔가 색이 다 빠져나간 느낌이에요. 가족들과의 일요일 저녁 식사에서도, 예전에 좋아하던 미술 작품을 볼 때도, 별로 아무것도 느껴지지 않아요. 그리고 가끔은 이유를 정확히 설명할 수는 없는데 눈물을 참느라 애써야 할 때도 있어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 이렇게 가라앉고 다른 일들과 단절된 느낌을 얼마나 오래 느껴오셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 이제 2년이 조금 넘었어요—시어머니가 저희 집으로 들어오신 이후부터요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 지난 2년 동안, 2개월 이상 평소의 자신으로 돌아왔다고 느낀 시기가 있었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 아니요, 그렇게 오래 예전의 저로 돌아왔다고 느낀 적은 없었어요. 시어머니가 들어오신 이후로 계속 이랬어요, 2년이 조금 넘었네요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 2년 전 이 일이 시작되기 전에도 살면서 상당히 우울했던 시기가 있었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] 잘 모르겠어요. 이런 느낌이었던 다른 시기는 딱히 떠오르지 않아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사 질문] 이 기간 동안 무가치감이나 과도한 죄책감으로 힘드셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 환자 응답] 잘 모르겠어요. 특별히 죄책감이나 무가치감을 느낀 적은 없는 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사 질문] 삶이 살 가치가 없다는 생각이나 자해에 대한 생각을 하신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 환자 응답] 정확히 무슨 뜻이신지 잘 모르겠어요. 그런 생각을 한 적은 딱히 없는 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011); 지속성 우울장애 (D014); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사 질문] 이 기간 동안 식욕이나 체중에 변화가 있으셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 환자 응답] 네. 요즘엔 식욕이 그다지 없어요. 대부분 다른 사람들을 위해 만든 음식을 조금씩 집어 먹거나, 근무 끝나고 토스트 정도 먹어요. 옷이 점점 헐렁해지고 있는데, 일부러 살을 빼려던 게 아니었어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사의 감별진단] 고확률: 지속성 우울장애 (D014) | 중간확률: 범불안장애 (D011); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사 질문] 집중하거나 초점을 맞추거나 일상적인 결정을 내리는 데 어려움을 느끼신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 환자 응답] 딱히 그런 실질적인 문제를 느낀 것 같지는 않아요. 그러니까, 평소 결정 같은 건 그럭저럭 해나가고 있어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사의 감별진단] 고확률: 지속성 우울장애 (D014) | 중간확률: 범불안장애 (D011); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사 질문] 본인이나 주변 사람들이 평소보다 움직임이나 말이 훨씬 느려졌다고 느낀 적이 있나요, 아니면 반대로 이유 없이 안절부절못하고 가만히 있지 못하는 느낌이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 환자 응답] 제가 움직이거나 말하는 게 느려졌다고 느낀 적은 없어요. 그리고 특별히 안절부절못하는 느낌도 없고요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사의 감별진단] 고확률: 지속성 우울장애 (D014) | 중간확률: 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사 질문] 미래에 대해 절망적이거나 상황이 나아지지 않을 거라는 느낌이 드시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 환자 응답] 네, 그런 것 같아요. 대부분의 날에는 모든 것에서 색이 빠져나간 느낌이에요. 가족들과의 일요일 저녁 식사에서도, 예전에 좋아하던 미술 작품을 볼 때도, 그냥... 무덤덤해요. 그리고 이유 없이 눈물이 나려는 걸 참으려고 애써야 해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사의 감별진단] 고확률: 지속성 우울장애 (D014) | 중간확률: 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사 질문] 수면이 끊기는 것 외에도, 낮 동안 에너지가 낮거나 지속적으로 피로감을 느끼신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 환자 응답] 네. 재택 간병 고객분들 보고 집에 돌아와서 그쪽 일까지 도와드리고 나면, 몸이 정말 무겁게 느껴져요. 차팅을 하거나 빨래를 개는 것도 억지로 해야 할 만큼 힘들게 느껴져요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사의 감별진단] 고확률: 지속성 우울장애 (D014) | 중간확률: 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 의사 질문] 이 기간 동안 자존감이나 자신감은 어떠셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 환자 응답] 어떻게 판단해야 할지 잘 모르겠어요. 그냥 요즘 스스로에 대해 좋게 느끼는 게 힘들다는 것만 알아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 의사의 감별진단] 고확률: 지속성 우울장애 (D014) | 중간확률: 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 의사 질문] 평소보다 훨씬 적은 수면으로도 괜찮을 만큼 비정상적으로 들뜨거나 활력이 넘치는 시기가 있으셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 환자 응답] 그런 것 같지 않아요. 비정상적으로 들뜨거나 잠을 거의 필요로 하지 않았던 시기는 기억나지 않아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
+배경 서술: 2년 4개월 전, 란의 시어머니의 건강이 악화되면서 란과 남편의 집으로 들어오게 되었고, 이는 유급 재택 간병 근무가 끝난 후 란의 전문 간병 기술을 24시간 가족 책임으로 바꾸어 놓았다. 처음에 란은 이 변화를 자신의 가족 가치관에 맞는 당연한 의무로 받아들였지만, 시간이 지나면서 박물관 방문, 등산, 서예, 자원봉사 미술 워크숍이 점차 밀려났고, 기분은 계속 가라앉아 있었으며, 식습관과 수면 패턴이 바뀌었고, 피로감이 직장과 집 양쪽에서 그녀를 따라다녔다. 그녀가 신입 요양보호사 멘토링을 줄이고 평소와 다르게 서류 작성을 미루기 시작하면서 상태는 임상적으로 유의미해졌고, 남편은 매주 이어지던 가족 저녁 식사조차 더 이상 그녀를 회복시켜주지 못한다는 것을 알아차렸다. 지속적인 탈진을 이유로 한 1차 진료 방문이 의뢰로 이어지면서 그녀는 정신과 진료를 받게 되었고, 그 시점에서 기능 손상을 동반한 2년 4개월간의 지속적인 우울 경과가 명확해졌다.
+표집된 증상 목록:
+  - S024 우울한 기분: 슬프거나 공허하거나 절망적인 기분이 지속되는 상태.
+  - S026 체중/식욕 변화: 식욕이나 체중의 현저한 증가 또는 감소.
+  - S027 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.
+  - S029 피로: 휴식으로 호전되지 않는 지속적인 피로와 뚜렷한 에너지 저하.</t>
+        </is>
+      </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>[14번째 턴 · 의사의 감별진단] 고확률: 지속성 우울장애 (D014) | 중간확률: 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 배제됨: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 지속성 우울장애 (D014, ICD: F34.1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: dysthymic_symptoms (관계=must_include, 요구개수=3, 충족개수=6, 커버리지=1.0)
-  확인된 근거: 우울한 기분: 슬프거나 공허하거나 절망적인 기분이 지속되는 상태.; 체중/식욕 변화: 식욕이나 체중의 현저한 증가 또는 감소.; 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.; 피로: 휴식으로 호전되지 않는 지속적인 피로와 뚜렷한 에너지 저하.; 낮은 자존감: 자신을 무능하거나 무가치하다고 평가하는 지속적인 경향, 만성적으로 낮은 자기평가.; 절망감: 미래에 대한 희망이 없다는 절망적인 느낌.
-  누락: 사고력 저하: 사고력이나 집중력 저하, 또는 우유부단함.</t>
+          <t>의사의 최종 진단: 지속성 우울장애 (D014, ICD: F34.1)
+지속 기간 요건: None
+기능적 손상 요건: None
+추가 요건: None
+체크리스트 그룹: dysthymic_symptoms (관계=must_include, 요구개수=3, 충족개수=6, 커버리지=1.0)
+확인된 근거:
+  - 우울한 기분: 슬프거나 공허하거나 절망적인 기분이 지속되는 상태.
+  - 체중/식욕 변화: 식욕이나 체중의 현저한 증가 또는 감소.
+  - 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.
+  - 피로: 휴식으로 호전되지 않는 지속적인 피로와 뚜렷한 에너지 저하.
+  - 낮은 자존감: 자신을 무능하거나 무가치하다고 평가하는 지속적인 경향, 만성적으로 낮은 자기평가.
+  - 절망감: 미래에 대한 희망이 없다는 절망적인 느낌.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="A58:B58"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D014_S002_P001__gemini-3.8-flash_kor.xlsx
+++ b/human_validation/judge/kor/judge_D014_S002_P001__gemini-3.8-flash_kor.xlsx
@@ -859,6 +859,11 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -899,11 +904,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A58:B58"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D014_S002_P001__gemini-3.8-flash_kor.xlsx
+++ b/human_validation/judge/kor/judge_D014_S002_P001__gemini-3.8-flash_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -472,7 +473,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.1883</v>
+        <v>0.4657</v>
       </c>
     </row>
     <row r="5">
@@ -492,7 +493,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.1994</v>
+        <v>0.6518</v>
       </c>
     </row>
     <row r="7">
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.6153999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>1</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
